--- a/stories/arbres/TREE-SEC-011.xlsx
+++ b/stories/arbres/TREE-SEC-011.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Noé est dans le salon. Maman est là. Ils sortent. Au chemin, il y a un feu. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de Maman. Maman est l'adulte. Papa prend le manteau.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon jaune, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1653,6 +1680,11 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Noé prend le ballon jaune. Ils vont au chemin. Noé attend le feu vert. Pieds sur le trottoir en attendant. Main de Maman, l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1869,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|On attend quoi ? Le feu vert. Avec qui ?</t>
         </is>
       </c>
     </row>
@@ -2009,6 +2046,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé retient : feu vert, main, adulte, trottoir en attendant. La main est dans la main de Maman. On continue, avec Maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2197,6 +2239,11 @@
       <c r="AV7" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2365,6 +2412,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi Tom. La porte du salon claque doux. Tom est là, avec un adulte. Noé attend le feu vert. Main de Maman. Trottoir en attendant. La main est dans la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2551,6 +2603,11 @@
         <v>12</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2717,6 +2774,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Le vent est doux. C'est le matin. On attend le feu vert. Main de Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2879,6 +2941,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3045,6 +3112,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Les pas font toc toc. C'est après la sieste. Pieds sur le trottoir en attendant. Feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3207,6 +3279,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3373,6 +3450,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Un vélo sonne loin. C'est le soir. On avance avec Maman, l'adulte. Au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3535,6 +3617,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3701,6 +3788,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi Léa. Un oiseau chante. Léa est là, avec un adulte. Noé attend le feu vert. Main de Maman. Trottoir en attendant. La main est dans la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3887,6 +3979,11 @@
         <v>12</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4053,6 +4150,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Les pas font toc toc. C'est le matin. On attend le feu vert. Main de Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4215,6 +4317,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4381,6 +4488,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Un vélo sonne loin. C'est après la sieste. Pieds sur le trottoir en attendant. Feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4543,6 +4655,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4709,6 +4826,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Le manteau est chaud. C'est le soir. On avance avec Maman, l'adulte. Au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4871,6 +4993,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5037,6 +5164,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi Sami. Le vent est doux. Sami est là, avec un adulte. Noé attend le feu vert. Main de Maman. Trottoir en attendant. La main est dans la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5223,6 +5355,11 @@
         <v>12</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5389,6 +5526,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Un vélo sonne loin. C'est le matin. On attend le feu vert. Main de Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5551,6 +5693,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5717,6 +5864,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Le manteau est chaud. C'est après la sieste. Pieds sur le trottoir en attendant. Feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5879,6 +6031,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6045,6 +6202,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. La porte du salon claque doux. C'est le soir. On avance avec Maman, l'adulte. Au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6207,6 +6369,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6373,6 +6540,11 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Noé prend le seau bleu. Ils vont au chemin. Noé attend le feu vert. Pieds sur le trottoir en attendant. Main de Maman, l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6557,6 +6729,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|On attend quoi ? Le feu vert. Avec qui ?</t>
         </is>
       </c>
     </row>
@@ -6729,6 +6906,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé retient : feu vert, main, adulte, trottoir en attendant. La main est dans la main de Maman. On continue, avec Maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6917,6 +7099,11 @@
       <c r="AV35" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7085,6 +7272,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi Tom. Les pas font toc toc. Tom est là, avec un adulte. Noé attend le feu vert. Main de Maman. Trottoir en attendant. La main est dans la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7271,6 +7463,11 @@
         <v>12</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7437,6 +7634,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Les pas font toc toc. C'est le matin. On attend le feu vert. Main de Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7599,6 +7801,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7765,6 +7972,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Un vélo sonne loin. C'est après la sieste. Pieds sur le trottoir en attendant. Feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7927,6 +8139,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8093,6 +8310,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Le manteau est chaud. C'est le soir. On avance avec Maman, l'adulte. Au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8255,6 +8477,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8421,6 +8648,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi Léa. Un vélo sonne loin. Léa est là, avec un adulte. Noé attend le feu vert. Main de Maman. Trottoir en attendant. La main est dans la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8607,6 +8839,11 @@
         <v>12</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8773,6 +9010,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Un vélo sonne loin. C'est le matin. On attend le feu vert. Main de Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8935,6 +9177,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9101,6 +9348,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Le manteau est chaud. C'est après la sieste. Pieds sur le trottoir en attendant. Feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9263,6 +9515,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9429,6 +9686,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. La porte du salon claque doux. C'est le soir. On avance avec Maman, l'adulte. Au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9591,6 +9853,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9757,6 +10024,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi Sami. Le manteau est chaud. Sami est là, avec un adulte. Noé attend le feu vert. Main de Maman. Trottoir en attendant. La main est dans la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9943,6 +10215,11 @@
         <v>12</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10109,6 +10386,11 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Le manteau est chaud. C'est le matin. On attend le feu vert. Main de Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10271,6 +10553,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10437,6 +10724,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. La porte du salon claque doux. C'est après la sieste. Pieds sur le trottoir en attendant. Feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10599,6 +10891,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10765,6 +11062,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Un oiseau chante. C'est le soir. On avance avec Maman, l'adulte. Au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10927,6 +11229,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11093,6 +11400,11 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Noé prend le doudou. Ils vont au chemin. Noé attend le feu vert. Pieds sur le trottoir en attendant. Main de Maman, l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11277,6 +11589,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|On attend quoi ? Le feu vert. Avec qui ?</t>
         </is>
       </c>
     </row>
@@ -11449,6 +11766,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé retient : feu vert, main, adulte, trottoir en attendant. La main est dans la main de Maman. On continue, avec Maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11637,6 +11959,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -11805,6 +12132,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi Tom. La porte du salon claque doux. Tom est là, avec un adulte. Noé attend le feu vert. Main de Maman. Trottoir en attendant. La main est dans la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11991,6 +12323,11 @@
         <v>12</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12157,6 +12494,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Un vélo sonne loin. C'est le matin. On attend le feu vert. Main de Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12319,6 +12661,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12485,6 +12832,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Le manteau est chaud. C'est après la sieste. Pieds sur le trottoir en attendant. Feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12647,6 +12999,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12813,6 +13170,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. La porte du salon claque doux. C'est le soir. On avance avec Maman, l'adulte. Au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12975,6 +13337,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13141,6 +13508,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi Léa. Un oiseau chante. Léa est là, avec un adulte. Noé attend le feu vert. Main de Maman. Trottoir en attendant. La main est dans la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13327,6 +13699,11 @@
         <v>12</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13493,6 +13870,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Le manteau est chaud. C'est le matin. On attend le feu vert. Main de Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13655,6 +14037,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13821,6 +14208,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. La porte du salon claque doux. C'est après la sieste. Pieds sur le trottoir en attendant. Feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13983,6 +14375,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14149,6 +14546,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Un oiseau chante. C'est le soir. On avance avec Maman, l'adulte. Au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14311,6 +14713,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14477,6 +14884,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi Sami. Le vent est doux. Sami est là, avec un adulte. Noé attend le feu vert. Main de Maman. Trottoir en attendant. La main est dans la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14663,6 +15075,11 @@
         <v>12</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14829,6 +15246,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. La porte du salon claque doux. C'est le matin. On attend le feu vert. Main de Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14991,6 +15413,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15157,6 +15584,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Un oiseau chante. C'est après la sieste. Pieds sur le trottoir en attendant. Feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15319,6 +15751,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15485,6 +15922,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Le vent est doux. C'est le soir. On avance avec Maman, l'adulte. Au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15647,6 +16089,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15665,7 +16112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15696,6 +16143,13 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>ch2C: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SEC-011.xlsx
+++ b/stories/arbres/TREE-SEC-011.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Noé est dans le salon. Maman est là. Ils sortent. Au chemin, il y a un feu. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de Maman. Maman est l'adulte. Papa prend le manteau.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le ballon jaune, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1685,6 +1692,7 @@
           <t>narrateur|Noé prend le ballon jaune. Ils vont au chemin. Noé attend le feu vert. Pieds sur le trottoir en attendant. Main de Maman, l'adulte.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1876,6 +1884,7 @@
           <t>narrateur|On attend quoi ? Le feu vert. Avec qui ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2051,6 +2060,7 @@
           <t>narrateur|Oui. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé retient : feu vert, main, adulte, trottoir en attendant. La main est dans la main de Maman. On continue, avec Maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2246,6 +2256,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2417,6 +2428,7 @@
           <t>narrateur|Noé a choisi Tom. La porte du salon claque doux. Tom est là, avec un adulte. Noé attend le feu vert. Main de Maman. Trottoir en attendant. La main est dans la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2608,6 +2620,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2779,6 +2792,7 @@
           <t>narrateur|C'est le matin. Le vent est doux. C'est le matin. On attend le feu vert. Main de Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2946,6 +2960,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3117,6 +3132,7 @@
           <t>narrateur|C'est après la sieste. Les pas font toc toc. C'est après la sieste. Pieds sur le trottoir en attendant. Feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3284,6 +3300,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3455,6 +3472,7 @@
           <t>narrateur|C'est le soir. Un vélo sonne loin. C'est le soir. On avance avec Maman, l'adulte. Au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3622,6 +3640,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3793,6 +3812,7 @@
           <t>narrateur|Noé a choisi Léa. Un oiseau chante. Léa est là, avec un adulte. Noé attend le feu vert. Main de Maman. Trottoir en attendant. La main est dans la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3984,6 +4004,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4155,6 +4176,7 @@
           <t>narrateur|C'est le matin. Les pas font toc toc. C'est le matin. On attend le feu vert. Main de Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4322,6 +4344,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4493,6 +4516,7 @@
           <t>narrateur|C'est après la sieste. Un vélo sonne loin. C'est après la sieste. Pieds sur le trottoir en attendant. Feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4660,6 +4684,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4831,6 +4856,7 @@
           <t>narrateur|C'est le soir. Le manteau est chaud. C'est le soir. On avance avec Maman, l'adulte. Au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4998,6 +5024,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5169,6 +5196,7 @@
           <t>narrateur|Noé a choisi Sami. Le vent est doux. Sami est là, avec un adulte. Noé attend le feu vert. Main de Maman. Trottoir en attendant. La main est dans la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5360,6 +5388,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5531,6 +5560,7 @@
           <t>narrateur|C'est le matin. Un vélo sonne loin. C'est le matin. On attend le feu vert. Main de Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5698,6 +5728,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5869,6 +5900,7 @@
           <t>narrateur|C'est après la sieste. Le manteau est chaud. C'est après la sieste. Pieds sur le trottoir en attendant. Feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6036,6 +6068,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6207,6 +6240,7 @@
           <t>narrateur|C'est le soir. La porte du salon claque doux. C'est le soir. On avance avec Maman, l'adulte. Au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6374,6 +6408,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6545,6 +6580,7 @@
           <t>narrateur|Noé prend le seau bleu. Ils vont au chemin. Noé attend le feu vert. Pieds sur le trottoir en attendant. Main de Maman, l'adulte.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6736,6 +6772,7 @@
           <t>narrateur|On attend quoi ? Le feu vert. Avec qui ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6911,6 +6948,7 @@
           <t>narrateur|Oui. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé retient : feu vert, main, adulte, trottoir en attendant. La main est dans la main de Maman. On continue, avec Maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7106,6 +7144,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7277,6 +7316,7 @@
           <t>narrateur|Noé a choisi Tom. Les pas font toc toc. Tom est là, avec un adulte. Noé attend le feu vert. Main de Maman. Trottoir en attendant. La main est dans la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7468,6 +7508,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7639,6 +7680,7 @@
           <t>narrateur|C'est le matin. Les pas font toc toc. C'est le matin. On attend le feu vert. Main de Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7806,6 +7848,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7977,6 +8020,7 @@
           <t>narrateur|C'est après la sieste. Un vélo sonne loin. C'est après la sieste. Pieds sur le trottoir en attendant. Feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8144,6 +8188,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8315,6 +8360,7 @@
           <t>narrateur|C'est le soir. Le manteau est chaud. C'est le soir. On avance avec Maman, l'adulte. Au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8482,6 +8528,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8653,6 +8700,7 @@
           <t>narrateur|Noé a choisi Léa. Un vélo sonne loin. Léa est là, avec un adulte. Noé attend le feu vert. Main de Maman. Trottoir en attendant. La main est dans la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8844,6 +8892,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -9015,6 +9064,7 @@
           <t>narrateur|C'est le matin. Un vélo sonne loin. C'est le matin. On attend le feu vert. Main de Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9182,6 +9232,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9353,6 +9404,7 @@
           <t>narrateur|C'est après la sieste. Le manteau est chaud. C'est après la sieste. Pieds sur le trottoir en attendant. Feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9520,6 +9572,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9691,6 +9744,7 @@
           <t>narrateur|C'est le soir. La porte du salon claque doux. C'est le soir. On avance avec Maman, l'adulte. Au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9858,6 +9912,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -10029,6 +10084,7 @@
           <t>narrateur|Noé a choisi Sami. Le manteau est chaud. Sami est là, avec un adulte. Noé attend le feu vert. Main de Maman. Trottoir en attendant. La main est dans la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10220,6 +10276,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10391,6 +10448,7 @@
           <t>narrateur|C'est le matin. Le manteau est chaud. C'est le matin. On attend le feu vert. Main de Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10558,6 +10616,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10729,6 +10788,7 @@
           <t>narrateur|C'est après la sieste. La porte du salon claque doux. C'est après la sieste. Pieds sur le trottoir en attendant. Feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10896,6 +10956,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11067,6 +11128,7 @@
           <t>narrateur|C'est le soir. Un oiseau chante. C'est le soir. On avance avec Maman, l'adulte. Au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11234,6 +11296,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11405,6 +11468,7 @@
           <t>narrateur|Noé prend le doudou. Ils vont au chemin. Noé attend le feu vert. Pieds sur le trottoir en attendant. Main de Maman, l'adulte.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11596,6 +11660,7 @@
           <t>narrateur|On attend quoi ? Le feu vert. Avec qui ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11771,6 +11836,7 @@
           <t>narrateur|Oui. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé retient : feu vert, main, adulte, trottoir en attendant. La main est dans la main de Maman. On continue, avec Maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11966,6 +12032,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12137,6 +12204,7 @@
           <t>narrateur|Noé a choisi Tom. La porte du salon claque doux. Tom est là, avec un adulte. Noé attend le feu vert. Main de Maman. Trottoir en attendant. La main est dans la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12328,6 +12396,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12499,6 +12568,7 @@
           <t>narrateur|C'est le matin. Un vélo sonne loin. C'est le matin. On attend le feu vert. Main de Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12666,6 +12736,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12837,6 +12908,7 @@
           <t>narrateur|C'est après la sieste. Le manteau est chaud. C'est après la sieste. Pieds sur le trottoir en attendant. Feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -13004,6 +13076,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13175,6 +13248,7 @@
           <t>narrateur|C'est le soir. La porte du salon claque doux. C'est le soir. On avance avec Maman, l'adulte. Au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13342,6 +13416,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13513,6 +13588,7 @@
           <t>narrateur|Noé a choisi Léa. Un oiseau chante. Léa est là, avec un adulte. Noé attend le feu vert. Main de Maman. Trottoir en attendant. La main est dans la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13704,6 +13780,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13875,6 +13952,7 @@
           <t>narrateur|C'est le matin. Le manteau est chaud. C'est le matin. On attend le feu vert. Main de Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -14042,6 +14120,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14213,6 +14292,7 @@
           <t>narrateur|C'est après la sieste. La porte du salon claque doux. C'est après la sieste. Pieds sur le trottoir en attendant. Feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14380,6 +14460,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14551,6 +14632,7 @@
           <t>narrateur|C'est le soir. Un oiseau chante. C'est le soir. On avance avec Maman, l'adulte. Au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14718,6 +14800,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14889,6 +14972,7 @@
           <t>narrateur|Noé a choisi Sami. Le vent est doux. Sami est là, avec un adulte. Noé attend le feu vert. Main de Maman. Trottoir en attendant. La main est dans la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -15080,6 +15164,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15251,6 +15336,7 @@
           <t>narrateur|C'est le matin. La porte du salon claque doux. C'est le matin. On attend le feu vert. Main de Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15418,6 +15504,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15589,6 +15676,7 @@
           <t>narrateur|C'est après la sieste. Un oiseau chante. C'est après la sieste. Pieds sur le trottoir en attendant. Feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15756,6 +15844,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15927,6 +16016,7 @@
           <t>narrateur|C'est le soir. Le vent est doux. C'est le soir. On avance avec Maman, l'adulte. Au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -16094,6 +16184,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16112,7 +16203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16150,6 +16241,20 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16164,7 +16269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16351,6 +16456,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
